--- a/data/informes/cuadro_10_1.xlsx
+++ b/data/informes/cuadro_10_1.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>116634350.08</v>
+        <v>116634350.94</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>54533631.84</v>
+        <v>54533632.56</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>0.4675610000000001</v>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>10666638.66</v>
+        <v>10666638.68</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>0.09145400000000001</v>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>17165983.36</v>
+        <v>17165983.39</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>0.147178</v>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>4697604.2</v>
+        <v>4697604.29</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>0.040276</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>152779410.83</v>
+        <v>152779411.69</v>
       </c>
       <c r="D40" s="10" t="n"/>
       <c r="E40" s="12" t="n">

--- a/data/informes/cuadro_10_1.xlsx
+++ b/data/informes/cuadro_10_1.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>116634350.94</v>
+        <v>116634350.2</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>54533632.56</v>
+        <v>54533631.98</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>0.4675610000000001</v>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>10666638.68</v>
+        <v>10666638.71</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>0.09145400000000001</v>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>17165983.39</v>
+        <v>17165983.46</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>0.147178</v>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>4697604.29</v>
+        <v>4697604.03</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>0.040276</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>152779411.69</v>
+        <v>152779410.95</v>
       </c>
       <c r="D40" s="10" t="n"/>
       <c r="E40" s="12" t="n">

--- a/data/informes/cuadro_10_1.xlsx
+++ b/data/informes/cuadro_10_1.xlsx
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>116634350.2</v>
+        <v>116418889.65</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.763417</v>
+        <v>0.7630830000000001</v>
       </c>
     </row>
     <row r="5">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>54533631.98</v>
+        <v>54454170.06</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.4675610000000001</v>
+        <v>0.467743</v>
       </c>
       <c r="E5" s="9" t="n"/>
     </row>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>27251708.68</v>
+        <v>26980076.04</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.233651</v>
+        <v>0.23175</v>
       </c>
       <c r="E6" s="9" t="n"/>
     </row>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>10666638.71</v>
+        <v>10650287.37</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.09145400000000001</v>
+        <v>0.09148199999999999</v>
       </c>
       <c r="E7" s="9" t="n"/>
     </row>
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>17165983.46</v>
+        <v>17317968.55</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.147178</v>
+        <v>0.148756</v>
       </c>
       <c r="E8" s="9" t="n"/>
     </row>
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>4697604.03</v>
+        <v>4697604.29</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.040276</v>
+        <v>0.040351</v>
       </c>
       <c r="E9" s="9" t="n"/>
     </row>
@@ -657,7 +657,7 @@
         <v>395573.23</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.003392</v>
+        <v>0.003398</v>
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
@@ -676,7 +676,7 @@
         <v>1627250.87</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.013952</v>
+        <v>0.013978</v>
       </c>
       <c r="E12" s="9" t="n"/>
     </row>
@@ -695,7 +695,7 @@
         <v>295959.24</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.002537</v>
+        <v>0.002542</v>
       </c>
       <c r="E13" s="9" t="n"/>
     </row>
@@ -736,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.067886</v>
+        <v>0.067982</v>
       </c>
     </row>
     <row r="16">
@@ -871,7 +871,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.107039</v>
+        <v>0.10719</v>
       </c>
     </row>
     <row r="23">
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.041547</v>
+        <v>0.041606</v>
       </c>
     </row>
     <row r="33">
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.01991</v>
+        <v>0.019938</v>
       </c>
     </row>
     <row r="37">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>152779410.95</v>
+        <v>152563950.4</v>
       </c>
       <c r="D40" s="10" t="n"/>
       <c r="E40" s="12" t="n">

--- a/data/informes/cuadro_10_1.xlsx
+++ b/data/informes/cuadro_10_1.xlsx
@@ -525,7 +525,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.7630830000000001</v>
+        <v>0.762813</v>
       </c>
     </row>
     <row r="5">
@@ -736,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.067982</v>
+        <v>0.067958</v>
       </c>
     </row>
     <row r="16">
@@ -871,7 +871,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.10719</v>
+        <v>0.107152</v>
       </c>
     </row>
     <row r="23">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>6347526.73</v>
+        <v>6401469.36</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.041606</v>
+        <v>0.041944</v>
       </c>
     </row>
     <row r="33">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>6347526.73</v>
+        <v>6401469.36</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>1</v>
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.019938</v>
+        <v>0.019931</v>
       </c>
     </row>
     <row r="37">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>152563950.4</v>
+        <v>152617893.03</v>
       </c>
       <c r="D40" s="10" t="n"/>
       <c r="E40" s="12" t="n">
